--- a/RAW_DATA_XLSX/PAK_raw_data.xlsx
+++ b/RAW_DATA_XLSX/PAK_raw_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,52 +429,57 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>BX.KLT.DINV.WD.GD.ZS</t>
+          <t>education</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>FP.CPI.TOTL.ZG</t>
+          <t>fdi</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>NE.TRD.GNFS.ZS</t>
+          <t>gdp_growth</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>NV.IND.TOTL.ZS</t>
+          <t>gdp_pc</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>NY.GDP.MKTP.KD.ZG</t>
+          <t>log_gdp_pc</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>NY.GDP.PCAP.KD</t>
+          <t>gini</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>SE.SEC.ENRR</t>
+          <t>industry</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>SI.POV.GINI</t>
+          <t>inflation</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>SL.UEM.TOTL.ZS</t>
+          <t>trade</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>SP.URB.TOTL.IN.ZS</t>
+          <t>unemployment</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>urban</t>
         </is>
       </c>
     </row>
@@ -487,30 +492,33 @@
       <c r="B2" t="n">
         <v>1995</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
         <v>1.19175194004056</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
+        <v>4.96260914623281</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1028.96592446155</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.936309620088013</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>21.3232921847751</v>
+      </c>
+      <c r="J2" t="n">
         <v>12.3435785170513</v>
       </c>
-      <c r="E2" t="n">
+      <c r="K2" t="n">
         <v>36.132753673519</v>
       </c>
-      <c r="F2" t="n">
-        <v>21.3232921847751</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4.96260914623281</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1028.96592446155</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>0.611</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>31.9144613917436</v>
       </c>
     </row>
@@ -523,32 +531,35 @@
       <c r="B3" t="n">
         <v>1996</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
         <v>1.45605449462756</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
+        <v>4.84658128681654</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1047.88663514614</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6.954530686459436</v>
+      </c>
+      <c r="H3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>21.9943844205166</v>
+      </c>
+      <c r="J3" t="n">
         <v>10.3738085885002</v>
       </c>
-      <c r="E3" t="n">
+      <c r="K3" t="n">
         <v>38.3301268339895</v>
       </c>
-      <c r="F3" t="n">
-        <v>21.9943844205166</v>
-      </c>
-      <c r="G3" t="n">
-        <v>4.84658128681654</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1047.88663514614</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>0.6</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>32.1402116675762</v>
       </c>
     </row>
@@ -561,30 +572,33 @@
       <c r="B4" t="n">
         <v>1997</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
         <v>1.14722858022912</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
+        <v>1.01439601077892</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1028.99804758369</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6.936340838440306</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>21.5572792952471</v>
+      </c>
+      <c r="J4" t="n">
         <v>11.3754928865122</v>
       </c>
-      <c r="E4" t="n">
+      <c r="K4" t="n">
         <v>36.8522661008964</v>
       </c>
-      <c r="F4" t="n">
-        <v>21.5572792952471</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.01439601077892</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1028.99804758369</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>0.611</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>32.3647607033211</v>
       </c>
     </row>
@@ -597,32 +611,35 @@
       <c r="B5" t="n">
         <v>1998</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
         <v>0.8136100455024839</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
+        <v>2.55023429817393</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1026.50033720969</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6.93391056496326</v>
+      </c>
+      <c r="H5" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>22.0530195066132</v>
+      </c>
+      <c r="J5" t="n">
         <v>6.22800415424543</v>
       </c>
-      <c r="E5" t="n">
+      <c r="K5" t="n">
         <v>34.011725180531</v>
       </c>
-      <c r="F5" t="n">
-        <v>22.0530195066132</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.55023429817393</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1026.50033720969</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>0.62</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>32.5871723893723</v>
       </c>
     </row>
@@ -635,30 +652,33 @@
       <c r="B6" t="n">
         <v>1999</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
         <v>0.84479500663461</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
+        <v>3.66013273943236</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1035.49888206288</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6.942638601224124</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>22.103173212169</v>
+      </c>
+      <c r="J6" t="n">
         <v>4.14263718082171</v>
       </c>
-      <c r="E6" t="n">
+      <c r="K6" t="n">
         <v>32.3199628094266</v>
       </c>
-      <c r="F6" t="n">
-        <v>22.103173212169</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3.66013273943236</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1035.49888206288</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>0.625</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>32.8015812487933</v>
       </c>
     </row>
@@ -671,30 +691,33 @@
       <c r="B7" t="n">
         <v>2000</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
         <v>0.309595026317044</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
+        <v>4.2600880111325</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1049.54229686852</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6.956109440371903</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>17.1836347813683</v>
+      </c>
+      <c r="J7" t="n">
         <v>4.36666451291681</v>
       </c>
-      <c r="E7" t="n">
+      <c r="K7" t="n">
         <v>21.4599638884654</v>
       </c>
-      <c r="F7" t="n">
-        <v>17.1836347813683</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4.2600880111325</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1049.54229686852</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>0.614</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>33.0046884491535</v>
       </c>
     </row>
@@ -707,32 +730,35 @@
       <c r="B8" t="n">
         <v>2001</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
         <v>0.38910658649849</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
+        <v>3.65135017083765</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1057.86767778646</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.964010536341795</v>
+      </c>
+      <c r="H8" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>17.5934942779914</v>
+      </c>
+      <c r="J8" t="n">
         <v>3.14826144590618</v>
       </c>
-      <c r="E8" t="n">
+      <c r="K8" t="n">
         <v>23.5772074298467</v>
       </c>
-      <c r="F8" t="n">
-        <v>17.5934942779914</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3.65135017083765</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1057.86767778646</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>0.611</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>33.1988471664032</v>
       </c>
     </row>
@@ -745,30 +771,33 @@
       <c r="B9" t="n">
         <v>2002</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
         <v>0.843517300073237</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
+        <v>2.59481668445784</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1059.04171024589</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.965119731271381</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>17.1588876671988</v>
+      </c>
+      <c r="J9" t="n">
         <v>3.29034472613153</v>
       </c>
-      <c r="E9" t="n">
+      <c r="K9" t="n">
         <v>23.1290159545291</v>
       </c>
-      <c r="F9" t="n">
-        <v>17.1588876671988</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.59481668445784</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1059.04171024589</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>0.615</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>33.3857078542752</v>
       </c>
     </row>
@@ -782,31 +811,34 @@
         <v>2003</v>
       </c>
       <c r="C10" t="n">
+        <v>19.8385200500488</v>
+      </c>
+      <c r="D10" t="n">
         <v>0.475207711805665</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
+        <v>5.40131087314342</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1090.27523993746</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6.994185457051062</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>17.3885833649452</v>
+      </c>
+      <c r="J10" t="n">
         <v>2.91413470059479</v>
       </c>
-      <c r="E10" t="n">
+      <c r="K10" t="n">
         <v>24.6501585248398</v>
       </c>
-      <c r="F10" t="n">
-        <v>17.3885833649452</v>
-      </c>
-      <c r="G10" t="n">
-        <v>5.40131087314342</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1090.27523993746</v>
-      </c>
-      <c r="I10" t="n">
-        <v>19.8385200500488</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>0.612</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>33.5669209665019</v>
       </c>
     </row>
@@ -820,33 +852,36 @@
         <v>2004</v>
       </c>
       <c r="C11" t="n">
+        <v>21.7634296417236</v>
+      </c>
+      <c r="D11" t="n">
         <v>0.845585701616171</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
+        <v>7.83125556961251</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1146.99632842666</v>
+      </c>
+      <c r="G11" t="n">
+        <v>7.044901916101283</v>
+      </c>
+      <c r="H11" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="I11" t="n">
+        <v>18.9071452885794</v>
+      </c>
+      <c r="J11" t="n">
         <v>7.44462469342739</v>
       </c>
-      <c r="E11" t="n">
+      <c r="K11" t="n">
         <v>24.8083348519064</v>
       </c>
-      <c r="F11" t="n">
-        <v>18.9071452885794</v>
-      </c>
-      <c r="G11" t="n">
-        <v>7.83125556961251</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1146.99632842666</v>
-      </c>
-      <c r="I11" t="n">
-        <v>21.7634296417236</v>
-      </c>
-      <c r="J11" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>0.598</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>33.7441369568158</v>
       </c>
     </row>
@@ -860,33 +895,36 @@
         <v>2005</v>
       </c>
       <c r="C12" t="n">
+        <v>22.6038208007812</v>
+      </c>
+      <c r="D12" t="n">
         <v>1.51575083116461</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
+        <v>7.2765744364722</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1201.23359367214</v>
+      </c>
+      <c r="G12" t="n">
+        <v>7.091104302478136</v>
+      </c>
+      <c r="H12" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>19.9330293059047</v>
+      </c>
+      <c r="J12" t="n">
         <v>9.063327370304171</v>
       </c>
-      <c r="E12" t="n">
+      <c r="K12" t="n">
         <v>29.8784940550747</v>
       </c>
-      <c r="F12" t="n">
-        <v>19.9330293059047</v>
-      </c>
-      <c r="G12" t="n">
-        <v>7.2765744364722</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1201.23359367214</v>
-      </c>
-      <c r="I12" t="n">
-        <v>22.6038208007812</v>
-      </c>
-      <c r="J12" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>0.583</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>33.9190062789495</v>
       </c>
     </row>
@@ -900,31 +938,34 @@
         <v>2006</v>
       </c>
       <c r="C13" t="n">
+        <v>27.2463207244873</v>
+      </c>
+      <c r="D13" t="n">
         <v>2.63975006245443</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
+        <v>6.05163767569996</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1243.94142602543</v>
+      </c>
+      <c r="G13" t="n">
+        <v>7.126040187002022</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>20.199119664936</v>
+      </c>
+      <c r="J13" t="n">
         <v>7.92108440058789</v>
       </c>
-      <c r="E13" t="n">
+      <c r="K13" t="n">
         <v>33.0497193672284</v>
       </c>
-      <c r="F13" t="n">
-        <v>20.199119664936</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6.05163767569996</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1243.94142602543</v>
-      </c>
-      <c r="I13" t="n">
-        <v>27.2463207244873</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>0.582</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>34.0931793866356</v>
       </c>
     </row>
@@ -938,33 +979,36 @@
         <v>2007</v>
       </c>
       <c r="C14" t="n">
+        <v>29.0634307861328</v>
+      </c>
+      <c r="D14" t="n">
         <v>3.03571933817685</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
+        <v>4.4448143398844</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1265.35567539842</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7.14310852796464</v>
+      </c>
+      <c r="H14" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>19.9449553163591</v>
+      </c>
+      <c r="J14" t="n">
         <v>7.59868441050774</v>
       </c>
-      <c r="E14" t="n">
+      <c r="K14" t="n">
         <v>30.7878814312746</v>
       </c>
-      <c r="F14" t="n">
-        <v>19.9449553163591</v>
-      </c>
-      <c r="G14" t="n">
-        <v>4.4448143398844</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1265.35567539842</v>
-      </c>
-      <c r="I14" t="n">
-        <v>29.0634307861328</v>
-      </c>
-      <c r="J14" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>0.398</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>34.2683067336065</v>
       </c>
     </row>
@@ -978,31 +1022,34 @@
         <v>2008</v>
       </c>
       <c r="C15" t="n">
+        <v>29.1768093109131</v>
+      </c>
+      <c r="D15" t="n">
         <v>2.68936656124595</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
+        <v>2.1204410433083</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1258.05188934452</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7.137319683901401</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>21.1955484525846</v>
+      </c>
+      <c r="J15" t="n">
         <v>20.2861210929554</v>
       </c>
-      <c r="E15" t="n">
+      <c r="K15" t="n">
         <v>34.3489608135242</v>
       </c>
-      <c r="F15" t="n">
-        <v>21.1955484525846</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2.1204410433083</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1258.05188934452</v>
-      </c>
-      <c r="I15" t="n">
-        <v>29.1768093109131</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>0.423</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>34.4460387735948</v>
       </c>
     </row>
@@ -1016,31 +1063,34 @@
         <v>2009</v>
       </c>
       <c r="C16" t="n">
+        <v>29.0589694976807</v>
+      </c>
+      <c r="D16" t="n">
         <v>1.24801305527951</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
+        <v>3.47255059567348</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1269.07432116444</v>
+      </c>
+      <c r="G16" t="n">
+        <v>7.146043032716872</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>20.3372467582902</v>
+      </c>
+      <c r="J16" t="n">
         <v>13.6477650639761</v>
       </c>
-      <c r="E16" t="n">
+      <c r="K16" t="n">
         <v>33.3268872863988</v>
       </c>
-      <c r="F16" t="n">
-        <v>20.3372467582902</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3.47255059567348</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1269.07432116444</v>
-      </c>
-      <c r="I16" t="n">
-        <v>29.0589694976807</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>0.535</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>34.6280259603331</v>
       </c>
     </row>
@@ -1054,33 +1104,36 @@
         <v>2010</v>
       </c>
       <c r="C17" t="n">
+        <v>29.2962900661933</v>
+      </c>
+      <c r="D17" t="n">
         <v>1.02791108080423</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
+        <v>1.50171752152883</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1256.69482201323</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7.136240396308027</v>
+      </c>
+      <c r="H17" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="I17" t="n">
+        <v>20.9650197800876</v>
+      </c>
+      <c r="J17" t="n">
         <v>12.9388705634889</v>
       </c>
-      <c r="E17" t="n">
+      <c r="K17" t="n">
         <v>31.9890020462315</v>
       </c>
-      <c r="F17" t="n">
-        <v>20.9650197800876</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.50171752152883</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1256.69482201323</v>
-      </c>
-      <c r="I17" t="n">
-        <v>29.2962900661933</v>
-      </c>
-      <c r="J17" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>0.653</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>34.8159187475539</v>
       </c>
     </row>
@@ -1094,33 +1147,36 @@
         <v>2011</v>
       </c>
       <c r="C18" t="n">
+        <v>29.7271460529531</v>
+      </c>
+      <c r="D18" t="n">
         <v>0.575055145839944</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
+        <v>2.68011685421705</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1261.83161907857</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7.140319610331392</v>
+      </c>
+      <c r="H18" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>21.1864809532945</v>
+      </c>
+      <c r="J18" t="n">
         <v>11.9160927116277</v>
       </c>
-      <c r="E18" t="n">
+      <c r="K18" t="n">
         <v>32.3626382751438</v>
       </c>
-      <c r="F18" t="n">
-        <v>21.1864809532945</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2.68011685421705</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1261.83161907857</v>
-      </c>
-      <c r="I18" t="n">
-        <v>29.7271460529531</v>
-      </c>
-      <c r="J18" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>0.796</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>35.0113675889897</v>
       </c>
     </row>
@@ -1134,31 +1190,34 @@
         <v>2012</v>
       </c>
       <c r="C19" t="n">
+        <v>30.6300201416016</v>
+      </c>
+      <c r="D19" t="n">
         <v>0.343453048660945</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
+        <v>3.02758391088629</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1275.48806898966</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7.151084183551179</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>21.9583720724829</v>
+      </c>
+      <c r="J19" t="n">
         <v>9.682351860556841</v>
       </c>
-      <c r="E19" t="n">
+      <c r="K19" t="n">
         <v>31.3189732760076</v>
       </c>
-      <c r="F19" t="n">
-        <v>21.9583720724829</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3.02758391088629</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1275.48806898966</v>
-      </c>
-      <c r="I19" t="n">
-        <v>30.6300201416016</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>3.667</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>35.2160229383731</v>
       </c>
     </row>
@@ -1172,33 +1231,36 @@
         <v>2013</v>
       </c>
       <c r="C20" t="n">
+        <v>31.544819132504</v>
+      </c>
+      <c r="D20" t="n">
         <v>0.515353849332245</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
+        <v>4.36686504978387</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1309.70080446386</v>
+      </c>
+      <c r="G20" t="n">
+        <v>7.177553996570383</v>
+      </c>
+      <c r="H20" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>20.8910295084645</v>
+      </c>
+      <c r="J20" t="n">
         <v>7.69215611899565</v>
       </c>
-      <c r="E20" t="n">
+      <c r="K20" t="n">
         <v>30.8902743401844</v>
       </c>
-      <c r="F20" t="n">
-        <v>20.8910295084645</v>
-      </c>
-      <c r="G20" t="n">
-        <v>4.36686504978387</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1309.70080446386</v>
-      </c>
-      <c r="I20" t="n">
-        <v>31.544819132504</v>
-      </c>
-      <c r="J20" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>2.954</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>35.4315352494366</v>
       </c>
     </row>
@@ -1212,31 +1274,34 @@
         <v>2014</v>
       </c>
       <c r="C21" t="n">
+        <v>32.6573427323505</v>
+      </c>
+      <c r="D21" t="n">
         <v>0.695308116834202</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
+        <v>4.11642817161422</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1343.30778121043</v>
+      </c>
+      <c r="G21" t="n">
+        <v>7.202890344660267</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>20.8659912298838</v>
+      </c>
+      <c r="J21" t="n">
         <v>7.18938402847028</v>
       </c>
-      <c r="E21" t="n">
+      <c r="K21" t="n">
         <v>29.4698256903998</v>
       </c>
-      <c r="F21" t="n">
-        <v>20.8659912298838</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4.11642817161422</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1343.30778121043</v>
-      </c>
-      <c r="I21" t="n">
-        <v>32.6573427323505</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>1.827</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>35.6595549759128</v>
       </c>
     </row>
@@ -1250,33 +1315,36 @@
         <v>2015</v>
       </c>
       <c r="C22" t="n">
+        <v>34.6741466548496</v>
+      </c>
+      <c r="D22" t="n">
         <v>0.5577343560321389</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
+        <v>4.21794209572506</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1380.47020838317</v>
+      </c>
+      <c r="G22" t="n">
+        <v>7.230179450828166</v>
+      </c>
+      <c r="H22" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>19.602614668814</v>
+      </c>
+      <c r="J22" t="n">
         <v>2.52932817254229</v>
       </c>
-      <c r="E22" t="n">
+      <c r="K22" t="n">
         <v>26.6881860172247</v>
       </c>
-      <c r="F22" t="n">
-        <v>19.602614668814</v>
-      </c>
-      <c r="G22" t="n">
-        <v>4.21794209572506</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1380.47020838317</v>
-      </c>
-      <c r="I22" t="n">
-        <v>34.6741466548496</v>
-      </c>
-      <c r="J22" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>3.566</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>35.9017325715342</v>
       </c>
     </row>
@@ -1290,31 +1358,34 @@
         <v>2016</v>
       </c>
       <c r="C23" t="n">
+        <v>35.8643246680809</v>
+      </c>
+      <c r="D23" t="n">
         <v>0.821349998064174</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
+        <v>6.57383828511043</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1452.18658269177</v>
+      </c>
+      <c r="G23" t="n">
+        <v>7.280825687605688</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>18.1501179723214</v>
+      </c>
+      <c r="J23" t="n">
         <v>3.7651191635658</v>
       </c>
-      <c r="E23" t="n">
+      <c r="K23" t="n">
         <v>24.7015780480573</v>
       </c>
-      <c r="F23" t="n">
-        <v>18.1501179723214</v>
-      </c>
-      <c r="G23" t="n">
-        <v>6.57383828511043</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1452.18658269177</v>
-      </c>
-      <c r="I23" t="n">
-        <v>35.8643246680809</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>2.285</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>36.1597184900333</v>
       </c>
     </row>
@@ -1328,31 +1399,34 @@
         <v>2017</v>
       </c>
       <c r="C24" t="n">
+        <v>35.3224248744451</v>
+      </c>
+      <c r="D24" t="n">
         <v>0.735837049658425</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
+        <v>4.43262590683975</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1495.26187528032</v>
+      </c>
+      <c r="G24" t="n">
+        <v>7.310056637896352</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>18.0993270885214</v>
+      </c>
+      <c r="J24" t="n">
         <v>4.08537368032608</v>
       </c>
-      <c r="E24" t="n">
+      <c r="K24" t="n">
         <v>25.472035002344</v>
       </c>
-      <c r="F24" t="n">
-        <v>18.0993270885214</v>
-      </c>
-      <c r="G24" t="n">
-        <v>4.43262590683975</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1495.26187528032</v>
-      </c>
-      <c r="I24" t="n">
-        <v>35.3224248744451</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>3.204</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>36.4351548223399</v>
       </c>
     </row>
@@ -1366,33 +1440,36 @@
         <v>2018</v>
       </c>
       <c r="C25" t="n">
+        <v>37.1466063259079</v>
+      </c>
+      <c r="D25" t="n">
         <v>0.487745750658143</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
+        <v>6.15170261099519</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1561.68169819559</v>
+      </c>
+      <c r="G25" t="n">
+        <v>7.3535185312701</v>
+      </c>
+      <c r="H25" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I25" t="n">
+        <v>18.5890515927482</v>
+      </c>
+      <c r="J25" t="n">
         <v>5.07805725868917</v>
       </c>
-      <c r="E25" t="n">
+      <c r="K25" t="n">
         <v>27.6260570796337</v>
       </c>
-      <c r="F25" t="n">
-        <v>18.5890515927482</v>
-      </c>
-      <c r="G25" t="n">
-        <v>6.15170261099519</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1561.68169819559</v>
-      </c>
-      <c r="I25" t="n">
-        <v>37.1466063259079</v>
-      </c>
-      <c r="J25" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>4.083</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>36.7478511550359</v>
       </c>
     </row>
@@ -1406,31 +1483,34 @@
         <v>2019</v>
       </c>
       <c r="C26" t="n">
+        <v>38.7511552822907</v>
+      </c>
+      <c r="D26" t="n">
         <v>0.696146480411465</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
+        <v>2.49763692943365</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1573.8330826937</v>
+      </c>
+      <c r="G26" t="n">
+        <v>7.36126937678076</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>19.5638945814483</v>
+      </c>
+      <c r="J26" t="n">
         <v>10.5780305672025</v>
       </c>
-      <c r="E26" t="n">
+      <c r="K26" t="n">
         <v>28.9055769867032</v>
       </c>
-      <c r="F26" t="n">
-        <v>19.5638945814483</v>
-      </c>
-      <c r="G26" t="n">
-        <v>2.49763692943365</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1573.8330826937</v>
-      </c>
-      <c r="I26" t="n">
-        <v>38.7511552822907</v>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>4.83</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>37.1091631735769</v>
       </c>
     </row>
@@ -1443,30 +1523,33 @@
       <c r="B27" t="n">
         <v>2020</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="n">
         <v>0.684695289874347</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
+        <v>-1.27408744338709</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1526.00597486307</v>
+      </c>
+      <c r="G27" t="n">
+        <v>7.330409127212275</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>18.5894635445816</v>
+      </c>
+      <c r="J27" t="n">
         <v>9.740116193201249</v>
       </c>
-      <c r="E27" t="n">
+      <c r="K27" t="n">
         <v>26.7162807328814</v>
       </c>
-      <c r="F27" t="n">
-        <v>18.5894635445816</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-1.27408744338709</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1526.00597486307</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>5.994</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>37.5080192948099</v>
       </c>
     </row>
@@ -1480,31 +1563,34 @@
         <v>2021</v>
       </c>
       <c r="C28" t="n">
+        <v>40.2578898404389</v>
+      </c>
+      <c r="D28" t="n">
         <v>0.616039439073827</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
+        <v>6.51388575852702</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1595.02792175422</v>
+      </c>
+      <c r="G28" t="n">
+        <v>7.374646520867739</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>18.8964082009484</v>
+      </c>
+      <c r="J28" t="n">
         <v>9.49641577285205</v>
       </c>
-      <c r="E28" t="n">
+      <c r="K28" t="n">
         <v>27.0304204125548</v>
       </c>
-      <c r="F28" t="n">
-        <v>18.8964082009484</v>
-      </c>
-      <c r="G28" t="n">
-        <v>6.51388575852702</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1595.02792175422</v>
-      </c>
-      <c r="I28" t="n">
-        <v>40.2578898404389</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>6.338</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>37.9333395514173</v>
       </c>
     </row>
@@ -1518,31 +1604,34 @@
         <v>2022</v>
       </c>
       <c r="C29" t="n">
+        <v>40.4177656413012</v>
+      </c>
+      <c r="D29" t="n">
         <v>0.389980753542853</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
+        <v>4.7781068690358</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1642.28066974826</v>
+      </c>
+      <c r="G29" t="n">
+        <v>7.403841207042412</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>20.4125955543613</v>
+      </c>
+      <c r="J29" t="n">
         <v>19.8738599646655</v>
       </c>
-      <c r="E29" t="n">
+      <c r="K29" t="n">
         <v>33.031353478032</v>
       </c>
-      <c r="F29" t="n">
-        <v>20.4125955543613</v>
-      </c>
-      <c r="G29" t="n">
-        <v>4.7781068690358</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1642.28066974826</v>
-      </c>
-      <c r="I29" t="n">
-        <v>40.4177656413012</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>5.291</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>38.3740439760816</v>
       </c>
     </row>
@@ -1556,31 +1645,34 @@
         <v>2023</v>
       </c>
       <c r="C30" t="n">
+        <v>42.2911451386891</v>
+      </c>
+      <c r="D30" t="n">
         <v>0.608281270820624</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
+        <v>-0.414935997088406</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1610.33122837537</v>
+      </c>
+      <c r="G30" t="n">
+        <v>7.384195168728769</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>20.718694602313</v>
+      </c>
+      <c r="J30" t="n">
         <v>30.7681280657005</v>
       </c>
-      <c r="E30" t="n">
+      <c r="K30" t="n">
         <v>28.4676925469837</v>
       </c>
-      <c r="F30" t="n">
-        <v>20.718694602313</v>
-      </c>
-      <c r="G30" t="n">
-        <v>-0.414935997088406</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1610.33122837537</v>
-      </c>
-      <c r="I30" t="n">
-        <v>42.2911451386891</v>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>5.237</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>38.8191861872791</v>
       </c>
     </row>
@@ -1594,33 +1686,36 @@
         <v>2024</v>
       </c>
       <c r="C31" t="n">
+        <v>48.2805022055997</v>
+      </c>
+      <c r="D31" t="n">
         <v>0.7166886452434</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
+        <v>3.04898287335465</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1634.56735260799</v>
+      </c>
+      <c r="G31" t="n">
+        <v>7.399133432172423</v>
+      </c>
+      <c r="H31" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>20.2457551236068</v>
+      </c>
+      <c r="J31" t="n">
         <v>12.6325318530452</v>
       </c>
-      <c r="E31" t="n">
+      <c r="K31" t="n">
         <v>27.5784683520695</v>
       </c>
-      <c r="F31" t="n">
-        <v>20.2457551236068</v>
-      </c>
-      <c r="G31" t="n">
-        <v>3.04898287335465</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1634.56735260799</v>
-      </c>
-      <c r="I31" t="n">
-        <v>48.2805022055997</v>
-      </c>
-      <c r="J31" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>5.492</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>39.1734368360905</v>
       </c>
     </row>
@@ -1641,10 +1736,11 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="n">
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
         <v>5.42</v>
       </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
